--- a/artfynd/A 25306-2026 artfynd.xlsx
+++ b/artfynd/A 25306-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134360564</v>
       </c>
       <c r="B2" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>134357013</v>
       </c>
       <c r="B3" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>134360572</v>
       </c>
       <c r="B5" t="n">
-        <v>96769</v>
+        <v>96776</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 25306-2026 artfynd.xlsx
+++ b/artfynd/A 25306-2026 artfynd.xlsx
@@ -675,51 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134360564</v>
+        <v>134360572</v>
       </c>
       <c r="B2" t="n">
-        <v>91988</v>
+        <v>96783</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Dåstorp, Dåstorp, Srm</t>
+          <t>Dåstorp, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>659917</v>
+        <v>659898</v>
       </c>
       <c r="R2" t="n">
-        <v>6556697</v>
+        <v>6556665</v>
       </c>
       <c r="S2" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -758,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,7 +789,7 @@
         <v>134357013</v>
       </c>
       <c r="B3" t="n">
-        <v>91988</v>
+        <v>91995</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134360551</v>
+        <v>134360564</v>
       </c>
       <c r="B4" t="n">
-        <v>57972</v>
+        <v>91995</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,31 +904,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -935,13 +931,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>659935</v>
+        <v>659917</v>
       </c>
       <c r="R4" t="n">
-        <v>6556806</v>
+        <v>6556697</v>
       </c>
       <c r="S4" t="n">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -970,7 +966,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -980,7 +976,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134360572</v>
+        <v>134360550</v>
       </c>
       <c r="B5" t="n">
-        <v>96776</v>
+        <v>57972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1018,28 +1014,36 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>bo, hörda ungar</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Dåstorp, Srm</t>
@@ -1081,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,7 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134360549</v>
+        <v>134360551</v>
       </c>
       <c r="B6" t="n">
-        <v>57969</v>
+        <v>57972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1129,21 +1133,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102977</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1157,17 +1161,17 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Dåstorp, Srm</t>
+          <t>Dåstorp, Dåstorp, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>659898</v>
+        <v>659935</v>
       </c>
       <c r="R6" t="n">
-        <v>6556665</v>
+        <v>6556806</v>
       </c>
       <c r="S6" t="n">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1196,7 +1200,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1206,7 +1210,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,27 +1237,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134360563</v>
+        <v>134360549</v>
       </c>
       <c r="B7" t="n">
-        <v>58698</v>
+        <v>57969</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103055</v>
+        <v>102977</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1311,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1321,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134360550</v>
+        <v>134360563</v>
       </c>
       <c r="B8" t="n">
-        <v>57972</v>
+        <v>58698</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>103055</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1383,11 +1387,7 @@
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>bo, hörda ungar</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 25306-2026 artfynd.xlsx
+++ b/artfynd/A 25306-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1003,60 +1003,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134360550</v>
+        <v>135445380</v>
       </c>
       <c r="B5" t="n">
-        <v>57972</v>
+        <v>91995</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>bo, hörda ungar</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Dåstorp, Srm</t>
+          <t>Långängen, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>659898</v>
+        <v>659913</v>
       </c>
       <c r="R5" t="n">
-        <v>6556665</v>
+        <v>6556700</v>
       </c>
       <c r="S5" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,22 +1068,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:25</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:25</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,22 +1088,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134360549</v>
+        <v>134360550</v>
       </c>
       <c r="B6" t="n">
-        <v>57969</v>
+        <v>57972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1133,21 +1111,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102977</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1157,7 +1135,11 @@
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>bo, hörda ungar</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1200,7 +1182,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1210,7 +1192,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,27 +1219,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134360563</v>
+        <v>134360549</v>
       </c>
       <c r="B7" t="n">
-        <v>58698</v>
+        <v>57969</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103055</v>
+        <v>102977</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1315,7 +1297,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1307,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,32 +1334,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134360551</v>
+        <v>134360563</v>
       </c>
       <c r="B8" t="n">
-        <v>57972</v>
+        <v>58698</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>103055</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1391,17 +1373,17 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Dåstorp, Dåstorp, Srm</t>
+          <t>Dåstorp, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>659935</v>
+        <v>659898</v>
       </c>
       <c r="R8" t="n">
-        <v>6556806</v>
+        <v>6556665</v>
       </c>
       <c r="S8" t="n">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1430,7 +1412,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1440,7 +1422,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,6 +1446,716 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135445379</v>
+      </c>
+      <c r="B9" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Långängen, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>659909</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6556716</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135445367</v>
+      </c>
+      <c r="B10" t="n">
+        <v>109896</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Långängen, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>659914</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6556664</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135445386</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99472</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kvarnbacken, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>659905</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6556635</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135445383</v>
+      </c>
+      <c r="B12" t="n">
+        <v>96410</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2812</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kransmossa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hylocomiadelphus triquetrus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Långängen, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>659976</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6556823</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134360551</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Dåstorp, Dåstorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>659935</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6556806</v>
+      </c>
+      <c r="S13" t="n">
+        <v>68</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anneli Ahlroth</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anneli Ahlroth</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135445369</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Långängen, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>659970</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6556790</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135445384</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99472</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Långängen, Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>659986</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6556878</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25306-2026 artfynd.xlsx
+++ b/artfynd/A 25306-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134360572</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134357013</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1000,6 +1015,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134360564</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1097,6 +1117,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445380</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1216,6 +1241,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134360550</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1331,6 +1361,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134360549</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1446,6 +1481,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134360563</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1543,6 +1583,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445379</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1653,6 +1698,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445367</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1750,6 +1800,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445386</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1847,6 +1902,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445383</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1962,6 +2022,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134360551</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2059,6 +2124,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445369</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2156,8 +2226,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445384</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 25306-2026 artfynd.xlsx
+++ b/artfynd/A 25306-2026 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>135445380</v>
       </c>
       <c r="B5" t="n">
-        <v>91995</v>
+        <v>92037</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>135445379</v>
       </c>
       <c r="B9" t="n">
-        <v>8460</v>
+        <v>8461</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>135445367</v>
       </c>
       <c r="B10" t="n">
-        <v>109896</v>
+        <v>109952</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>135445386</v>
       </c>
       <c r="B11" t="n">
-        <v>99472</v>
+        <v>99519</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>135445383</v>
       </c>
       <c r="B12" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>135445369</v>
       </c>
       <c r="B14" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>135445384</v>
       </c>
       <c r="B15" t="n">
-        <v>99472</v>
+        <v>99519</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 25306-2026 artfynd.xlsx
+++ b/artfynd/A 25306-2026 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>135445380</v>
       </c>
       <c r="B5" t="n">
-        <v>92037</v>
+        <v>92064</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>135445367</v>
       </c>
       <c r="B10" t="n">
-        <v>109952</v>
+        <v>109979</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>135445386</v>
       </c>
       <c r="B11" t="n">
-        <v>99519</v>
+        <v>99546</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>135445383</v>
       </c>
       <c r="B12" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>135445384</v>
       </c>
       <c r="B15" t="n">
-        <v>99519</v>
+        <v>99546</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 25306-2026 artfynd.xlsx
+++ b/artfynd/A 25306-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1023,60 +1023,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134360550</v>
+        <v>135445380</v>
       </c>
       <c r="B5" t="n">
-        <v>57972</v>
+        <v>92069</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>bo, hörda ungar</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Dåstorp, Srm</t>
+          <t>Långängen, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>659898</v>
+        <v>659913</v>
       </c>
       <c r="R5" t="n">
-        <v>6556665</v>
+        <v>6556700</v>
       </c>
       <c r="S5" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1100,22 +1088,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:25</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:25</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,27 +1108,27 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134360550</t>
+          <t>https://artportalen.se/Sighting/135445380</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134360549</v>
+        <v>134360550</v>
       </c>
       <c r="B6" t="n">
-        <v>57969</v>
+        <v>57972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1158,21 +1136,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102977</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1182,7 +1160,11 @@
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>bo, hörda ungar</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1225,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1235,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,33 +1243,33 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134360549</t>
+          <t>https://artportalen.se/Sighting/134360550</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134360563</v>
+        <v>134360549</v>
       </c>
       <c r="B7" t="n">
-        <v>58698</v>
+        <v>57969</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103055</v>
+        <v>102977</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1345,7 +1327,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,7 +1337,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,38 +1363,38 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134360563</t>
+          <t>https://artportalen.se/Sighting/134360549</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134360551</v>
+        <v>134360563</v>
       </c>
       <c r="B8" t="n">
-        <v>57972</v>
+        <v>58698</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>103055</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1426,17 +1408,17 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Dåstorp, Dåstorp, Srm</t>
+          <t>Dåstorp, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>659935</v>
+        <v>659898</v>
       </c>
       <c r="R8" t="n">
-        <v>6556806</v>
+        <v>6556665</v>
       </c>
       <c r="S8" t="n">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1465,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1475,7 +1457,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1501,7 +1483,752 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/134360563</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135445379</v>
+      </c>
+      <c r="B9" t="n">
+        <v>8461</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Långängen, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>659909</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6556716</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445379</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135445367</v>
+      </c>
+      <c r="B10" t="n">
+        <v>109984</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Långängen, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>659914</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6556664</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445367</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135445386</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99551</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kvarnbacken, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>659905</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6556635</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445386</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135445383</v>
+      </c>
+      <c r="B12" t="n">
+        <v>96486</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2812</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kransmossa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hylocomiadelphus triquetrus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Långängen, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>659976</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6556823</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445383</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134360551</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Dåstorp, Dåstorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>659935</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6556806</v>
+      </c>
+      <c r="S13" t="n">
+        <v>68</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anneli Ahlroth</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anneli Ahlroth</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/134360551</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135445369</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Långängen, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>659970</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6556790</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445369</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135445384</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99551</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Långängen, Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>659986</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6556878</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445384</t>
         </is>
       </c>
     </row>
@@ -1514,6 +2241,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25306-2026 artfynd.xlsx
+++ b/artfynd/A 25306-2026 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>135445380</v>
       </c>
       <c r="B5" t="n">
-        <v>92069</v>
+        <v>92071</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>135445367</v>
       </c>
       <c r="B10" t="n">
-        <v>109984</v>
+        <v>109986</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>135445386</v>
       </c>
       <c r="B11" t="n">
-        <v>99551</v>
+        <v>99553</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>135445383</v>
       </c>
       <c r="B12" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>135445384</v>
       </c>
       <c r="B15" t="n">
-        <v>99551</v>
+        <v>99553</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 25306-2026 artfynd.xlsx
+++ b/artfynd/A 25306-2026 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>135445380</v>
       </c>
       <c r="B5" t="n">
-        <v>92071</v>
+        <v>92085</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>135445379</v>
       </c>
       <c r="B9" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>135445367</v>
       </c>
       <c r="B10" t="n">
-        <v>109986</v>
+        <v>110009</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>135445386</v>
       </c>
       <c r="B11" t="n">
-        <v>99553</v>
+        <v>99570</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>135445383</v>
       </c>
       <c r="B12" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>135445369</v>
       </c>
       <c r="B14" t="n">
-        <v>58136</v>
+        <v>58138</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>135445384</v>
       </c>
       <c r="B15" t="n">
-        <v>99553</v>
+        <v>99570</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
